--- a/mappings/parameter_mapping_final.xlsx
+++ b/mappings/parameter_mapping_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ocean\Work\Projects\2026\ISC\Tools\Repositories\mappings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED61B445-1760-42C0-9680-BA7E60597990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55F7FD7-F3C6-4AE3-A8A1-38886982903B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="wadar_isc_cas" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="missing" sheetId="10" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">mapping!$A$1:$L$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">mapping!$A$1:$L$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">total_mapping!$A$1:$I$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">wadar_isc_cas!$A$1:$I$80</definedName>
   </definedNames>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3842" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3919" uniqueCount="509">
   <si>
     <t>Unieke identificatie gemeten parameter</t>
   </si>
@@ -1561,6 +1561,15 @@
   </si>
   <si>
     <t>Corg</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>s4C9yFol</t>
+  </si>
+  <si>
+    <t>IBD</t>
   </si>
 </sst>
 </file>
@@ -1662,7 +1671,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1710,6 +1719,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8349,7 +8359,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C99E872-61DA-4FE9-85D3-BDDE6515F002}">
-  <dimension ref="A1:L138"/>
+  <dimension ref="A1:L145"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.88671875" style="8" customWidth="1"/>
@@ -9431,33 +9441,38 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="12">
+      <c r="A32" s="8">
         <v>1198</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G32" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12" t="s">
-        <v>467</v>
+      <c r="G32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="8">
+        <v>1</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
@@ -10273,54 +10288,61 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" s="12">
+      <c r="A57" s="8">
         <v>1319</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C57" s="11" t="s">
         <v>440</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="E57" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12" t="s">
+      <c r="E57" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="G57" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
-      <c r="K57" s="12"/>
-      <c r="L57" s="12" t="s">
+      <c r="H57" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="I57" s="8">
+        <v>1</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K57" t="s">
         <v>467</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
-        <v>1335</v>
+        <v>1319</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>441</v>
+        <v>187</v>
       </c>
       <c r="G58" s="8" t="s">
         <v>190</v>
       </c>
       <c r="H58" t="s">
-        <v>504</v>
+        <v>185</v>
       </c>
       <c r="I58">
         <v>1</v>
@@ -10331,28 +10353,28 @@
       <c r="K58" t="s">
         <v>480</v>
       </c>
+      <c r="L58" s="8" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
-        <v>1337</v>
+        <v>1319</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>182</v>
+        <v>335</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>440</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>183</v>
+        <v>348</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>181</v>
+        <v>445</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H59" t="s">
         <v>185</v>
@@ -10364,30 +10386,33 @@
         <v>14</v>
       </c>
       <c r="K59" t="s">
-        <v>481</v>
+        <v>480</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>444</v>
+        <v>349</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>442</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H60" t="s">
-        <v>185</v>
+        <v>504</v>
       </c>
       <c r="I60">
         <v>1</v>
@@ -10396,30 +10421,30 @@
         <v>14</v>
       </c>
       <c r="K60" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H61" t="s">
         <v>185</v>
@@ -10431,27 +10456,27 @@
         <v>14</v>
       </c>
       <c r="K61" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>446</v>
+        <v>496</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H62" t="s">
         <v>185</v>
@@ -10463,116 +10488,129 @@
         <v>14</v>
       </c>
       <c r="K62" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>335</v>
+        <v>494</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>448</v>
+        <v>188</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>355</v>
+        <v>189</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>473</v>
+        <v>187</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="H63" t="s">
         <v>185</v>
       </c>
-      <c r="I63" s="8">
-        <v>0.1</v>
+      <c r="I63">
+        <v>1</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>447</v>
+        <v>14</v>
       </c>
       <c r="K63" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A64" s="12">
-        <v>1350</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>450</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>449</v>
-      </c>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="H64" s="12"/>
-      <c r="I64" s="12"/>
-      <c r="J64" s="12"/>
-      <c r="K64" s="12"/>
-      <c r="L64" s="12" t="s">
-        <v>467</v>
+      <c r="A64" s="8">
+        <v>1340</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="H64" t="s">
+        <v>185</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K64" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
-        <v>1361</v>
+        <v>1345</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>335</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>451</v>
+        <v>473</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H65" s="8" t="s">
-        <v>15</v>
+        <v>500</v>
+      </c>
+      <c r="H65" t="s">
+        <v>185</v>
       </c>
       <c r="I65" s="8">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K65" s="8" t="s">
-        <v>481</v>
+        <v>447</v>
+      </c>
+      <c r="K65" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
-        <v>1368</v>
+        <v>1350</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>335</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>453</v>
+        <v>357</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>449</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H66" s="8" t="s">
-        <v>15</v>
+        <v>184</v>
+      </c>
+      <c r="H66" t="s">
+        <v>185</v>
       </c>
       <c r="I66" s="8">
         <v>1</v>
@@ -10581,73 +10619,64 @@
         <v>14</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>1369</v>
-      </c>
-      <c r="B67" t="s">
-        <v>191</v>
-      </c>
-      <c r="C67" t="s">
-        <v>193</v>
-      </c>
-      <c r="D67" t="s">
-        <v>194</v>
-      </c>
-      <c r="E67" t="s">
-        <v>192</v>
-      </c>
-      <c r="F67" t="s">
-        <v>192</v>
-      </c>
-      <c r="G67" t="s">
-        <v>13</v>
+      <c r="A67" s="8">
+        <v>1350</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>184</v>
       </c>
       <c r="H67" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="I67" s="8">
         <v>1</v>
       </c>
-      <c r="J67" t="s">
+      <c r="J67" s="8" t="s">
         <v>14</v>
       </c>
       <c r="K67" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>1379</v>
-      </c>
-      <c r="B68" t="s">
-        <v>191</v>
-      </c>
-      <c r="C68" t="s">
-        <v>463</v>
-      </c>
-      <c r="D68" t="s">
-        <v>195</v>
-      </c>
-      <c r="E68" t="s">
-        <v>464</v>
-      </c>
-      <c r="F68" t="s">
-        <v>464</v>
-      </c>
-      <c r="G68" t="s">
-        <v>13</v>
-      </c>
-      <c r="H68" t="s">
+      <c r="A68" s="8">
+        <v>1361</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="8">
         <v>1</v>
       </c>
-      <c r="J68" t="s">
+      <c r="J68" s="8" t="s">
         <v>14</v>
       </c>
       <c r="K68" s="8" t="s">
@@ -10656,22 +10685,16 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
-        <v>1382</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>196</v>
+        <v>1368</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>198</v>
+        <v>454</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>199</v>
+        <v>359</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="F69" s="8" t="s">
-        <v>197</v>
+        <v>453</v>
       </c>
       <c r="G69" s="8" t="s">
         <v>13</v>
@@ -10690,31 +10713,34 @@
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70" s="8">
-        <v>1383</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H70" s="8" t="s">
+      <c r="A70">
+        <v>1369</v>
+      </c>
+      <c r="B70" t="s">
+        <v>191</v>
+      </c>
+      <c r="C70" t="s">
+        <v>193</v>
+      </c>
+      <c r="D70" t="s">
+        <v>194</v>
+      </c>
+      <c r="E70" t="s">
+        <v>192</v>
+      </c>
+      <c r="F70" t="s">
+        <v>192</v>
+      </c>
+      <c r="G70" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="8">
         <v>1</v>
       </c>
-      <c r="J70" s="8" t="s">
+      <c r="J70" t="s">
         <v>14</v>
       </c>
       <c r="K70" s="8" t="s">
@@ -10722,28 +10748,34 @@
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71" s="8">
-        <v>1385</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="D71" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H71" s="8" t="s">
+      <c r="A71">
+        <v>1379</v>
+      </c>
+      <c r="B71" t="s">
+        <v>191</v>
+      </c>
+      <c r="C71" t="s">
+        <v>463</v>
+      </c>
+      <c r="D71" t="s">
+        <v>195</v>
+      </c>
+      <c r="E71" t="s">
+        <v>464</v>
+      </c>
+      <c r="F71" t="s">
+        <v>464</v>
+      </c>
+      <c r="G71" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="8">
         <v>1</v>
       </c>
-      <c r="J71" s="8" t="s">
+      <c r="J71" t="s">
         <v>14</v>
       </c>
       <c r="K71" s="8" t="s">
@@ -10752,22 +10784,22 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G72" s="8" t="s">
         <v>13</v>
@@ -10787,22 +10819,19 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>204</v>
+        <v>497</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>206</v>
+        <v>456</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>207</v>
+        <v>361</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>205</v>
+        <v>455</v>
       </c>
       <c r="G73" s="8" t="s">
         <v>13</v>
@@ -10822,22 +10851,16 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
-        <v>1388</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>208</v>
+        <v>1385</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>210</v>
+        <v>458</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>211</v>
+        <v>362</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>209</v>
+        <v>457</v>
       </c>
       <c r="G74" s="8" t="s">
         <v>13</v>
@@ -10857,22 +10880,22 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="G75" s="8" t="s">
         <v>13</v>
@@ -10892,28 +10915,28 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
-        <v>1433</v>
+        <v>1387</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>220</v>
+        <v>13</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="I76" s="8">
         <v>1</v>
@@ -10921,28 +10944,28 @@
       <c r="J76" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K76" t="s">
-        <v>483</v>
+      <c r="K76" s="8" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
-        <v>1439</v>
+        <v>1388</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="G77" s="8" t="s">
         <v>13</v>
@@ -10957,27 +10980,27 @@
         <v>14</v>
       </c>
       <c r="K77" s="8" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
-        <v>1458</v>
+        <v>1392</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="G78" s="8" t="s">
         <v>13</v>
@@ -10992,33 +11015,33 @@
         <v>14</v>
       </c>
       <c r="K78" s="8" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
-        <v>1464</v>
+        <v>1433</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>13</v>
+        <v>220</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="I79" s="8">
         <v>1</v>
@@ -11026,28 +11049,28 @@
       <c r="J79" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K79" s="8" t="s">
-        <v>473</v>
+      <c r="K79" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
-        <v>1517</v>
+        <v>1439</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="G80" s="8" t="s">
         <v>13</v>
@@ -11067,25 +11090,28 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
-        <v>1551</v>
+        <v>1458</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>363</v>
+        <v>225</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>365</v>
+        <v>227</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>366</v>
+        <v>228</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>485</v>
+        <v>226</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>226</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="I81" s="8">
         <v>1</v>
@@ -11093,31 +11119,34 @@
       <c r="J81" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K81" t="s">
-        <v>467</v>
+      <c r="K81" s="8" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
-        <v>1551</v>
+        <v>1464</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>363</v>
+        <v>229</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>365</v>
+        <v>231</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>366</v>
+        <v>232</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>485</v>
+        <v>230</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="I82" s="8">
         <v>1</v>
@@ -11126,27 +11155,27 @@
         <v>14</v>
       </c>
       <c r="K82" s="8" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
-        <v>1629</v>
+        <v>1517</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G83" s="8" t="s">
         <v>13</v>
@@ -11166,28 +11195,25 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
-        <v>1630</v>
+        <v>1551</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>241</v>
+        <v>363</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>243</v>
+        <v>365</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>244</v>
+        <v>366</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="F84" s="8" t="s">
-        <v>242</v>
+        <v>485</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="I84" s="8">
         <v>1</v>
@@ -11195,34 +11221,31 @@
       <c r="J84" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K84" s="8" t="s">
-        <v>473</v>
+      <c r="K84" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
-        <v>1652</v>
+        <v>1551</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>245</v>
+        <v>363</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>247</v>
+        <v>365</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>248</v>
+        <v>366</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>246</v>
+        <v>485</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="I85" s="8">
         <v>1</v>
@@ -11231,27 +11254,27 @@
         <v>14</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
-        <v>1688</v>
+        <v>1629</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="G86" s="8" t="s">
         <v>13</v>
@@ -11270,48 +11293,58 @@
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A87" s="12">
-        <v>1743</v>
-      </c>
-      <c r="B87" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="C87" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="E87" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="F87" s="12"/>
-      <c r="G87" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H87" s="12"/>
-      <c r="I87" s="12"/>
-      <c r="J87" s="12"/>
-      <c r="K87" s="12"/>
-      <c r="L87" s="12" t="s">
-        <v>467</v>
+      <c r="A87" s="8">
+        <v>1630</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I87" s="8">
+        <v>1</v>
+      </c>
+      <c r="J87" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K87" s="8" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
-        <v>1774</v>
+        <v>1652</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>371</v>
+        <v>245</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>373</v>
+        <v>247</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="E88" t="s">
-        <v>242</v>
+        <v>248</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>246</v>
       </c>
       <c r="G88" s="8" t="s">
         <v>13</v>
@@ -11327,197 +11360,194 @@
       </c>
       <c r="K88" s="8" t="s">
         <v>473</v>
-      </c>
-      <c r="L88" s="8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
+        <v>1688</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H89" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" s="8">
+        <v>1</v>
+      </c>
+      <c r="J89" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K89" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90" s="12">
+        <v>1743</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="F90" s="12"/>
+      <c r="G90" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H90" s="12"/>
+      <c r="I90" s="12"/>
+      <c r="J90" s="12"/>
+      <c r="K90" s="12"/>
+      <c r="L90" s="12" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" s="8">
         <v>1774</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B91" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C91" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="D89" s="8" t="s">
+      <c r="D91" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="E89" s="8" t="s">
+      <c r="E91" t="s">
+        <v>242</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H91" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I91" s="8">
+        <v>1</v>
+      </c>
+      <c r="J91" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K91" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="L91" s="8" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" s="8">
+        <v>1774</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="E92" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="G89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H89" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" s="8">
-        <v>1</v>
-      </c>
-      <c r="J89" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K89" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="L89" s="8" t="s">
+      <c r="G92" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H92" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I92" s="8">
+        <v>1</v>
+      </c>
+      <c r="J92" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K92" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="L92" s="8" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A90" s="8">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A93" s="8">
         <v>1774</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B93" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C93" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="D90" s="8" t="s">
+      <c r="D93" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E93" t="s">
         <v>238</v>
       </c>
-      <c r="G90" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H90" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I90" s="8">
-        <v>1</v>
-      </c>
-      <c r="J90" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K90" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="L90" s="8" t="s">
+      <c r="G93" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" s="8">
+        <v>1</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K93" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="L93" s="8" t="s">
         <v>490</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="8">
-        <v>1877</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="G91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H91" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I91" s="8">
-        <v>1</v>
-      </c>
-      <c r="J91" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K91" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="8">
-        <v>1888</v>
-      </c>
-      <c r="B92" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="C92" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="G92" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H92" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I92" s="8">
-        <v>1</v>
-      </c>
-      <c r="J92" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K92" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A93" s="12">
-        <v>1920</v>
-      </c>
-      <c r="B93" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="C93" s="14" t="s">
-        <v>377</v>
-      </c>
-      <c r="D93" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="E93" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="F93" s="12"/>
-      <c r="G93" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H93" s="12"/>
-      <c r="I93" s="12"/>
-      <c r="J93" s="12"/>
-      <c r="K93" s="12"/>
-      <c r="L93" s="12" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="8">
-        <v>1935</v>
+        <v>1877</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="G94" s="8" t="s">
         <v>13</v>
@@ -11536,48 +11566,55 @@
       </c>
     </row>
     <row r="95" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="12">
-        <v>1955</v>
-      </c>
-      <c r="B95" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="C95" s="14" t="s">
-        <v>381</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="E95" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="F95" s="12"/>
-      <c r="G95" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="8">
+        <v>1888</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I95" s="8">
+        <v>1</v>
+      </c>
+      <c r="J95" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K95" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="12">
-        <v>1958</v>
+        <v>1920</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="F96" s="12"/>
       <c r="G96" s="12" t="s">
@@ -11591,129 +11628,115 @@
         <v>467</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="8">
+        <v>1935</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="8">
+        <v>1</v>
+      </c>
+      <c r="J97" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K97" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="12">
+        <v>1955</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="E98" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="F98" s="12"/>
+      <c r="G98" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H98" s="12"/>
+      <c r="I98" s="12"/>
+      <c r="J98" s="12"/>
+      <c r="K98" s="12"/>
+      <c r="L98" s="12" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="12">
+        <v>1958</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H99" s="12"/>
+      <c r="I99" s="12"/>
+      <c r="J99" s="12"/>
+      <c r="K99" s="12"/>
+      <c r="L99" s="12" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A100" s="8">
         <v>1959</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B100" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="C97" s="9" t="s">
+      <c r="C100" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="D97" s="8" t="s">
+      <c r="D100" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="E97" s="8" t="s">
+      <c r="E100" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="F97" s="8" t="s">
+      <c r="F100" s="8" t="s">
         <v>264</v>
-      </c>
-      <c r="G97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H97" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I97" s="8">
-        <v>1</v>
-      </c>
-      <c r="J97" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K97" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" s="8">
-        <v>2028</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="G98" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H98" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I98" s="8">
-        <v>1</v>
-      </c>
-      <c r="J98" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K98" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A99" s="8">
-        <v>2879</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="D99" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="G99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H99" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="I99" s="8">
-        <v>1E-3</v>
-      </c>
-      <c r="J99" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K99" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="8">
-        <v>2911</v>
-      </c>
-      <c r="B100" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="D100" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="F100" s="8" t="s">
-        <v>277</v>
       </c>
       <c r="G100" s="8" t="s">
         <v>13</v>
@@ -11733,22 +11756,22 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="8">
-        <v>2912</v>
+        <v>2028</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="E101" s="9" t="s">
-        <v>281</v>
+        <v>270</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>268</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="G101" s="8" t="s">
         <v>13</v>
@@ -11768,31 +11791,31 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
-        <v>2915</v>
+        <v>2879</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="G102" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>15</v>
+        <v>275</v>
       </c>
       <c r="I102" s="8">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="J102" s="8" t="s">
         <v>14</v>
@@ -11801,24 +11824,24 @@
         <v>473</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="8">
-        <v>2916</v>
+        <v>2911</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>288</v>
+        <v>495</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="G103" s="8" t="s">
         <v>13</v>
@@ -11838,22 +11861,22 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
-        <v>2919</v>
+        <v>2912</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>293</v>
+        <v>283</v>
+      </c>
+      <c r="E104" s="9" t="s">
+        <v>281</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="G104" s="8" t="s">
         <v>13</v>
@@ -11873,22 +11896,22 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
-        <v>2920</v>
+        <v>2915</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="G105" s="8" t="s">
         <v>13</v>
@@ -11908,25 +11931,25 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
-        <v>5347</v>
+        <v>2916</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>472</v>
+        <v>13</v>
       </c>
       <c r="H106" s="8" t="s">
         <v>15</v>
@@ -11942,56 +11965,66 @@
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A107" s="12">
-        <v>5474</v>
-      </c>
-      <c r="B107" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="C107" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="D107" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="E107" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="F107" s="12"/>
-      <c r="G107" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
-      <c r="L107" s="12" t="s">
-        <v>467</v>
+      <c r="A107" s="8">
+        <v>2919</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H107" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I107" s="8">
+        <v>1</v>
+      </c>
+      <c r="J107" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K107" s="8" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
-        <v>5534</v>
+        <v>2920</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>469</v>
+        <v>296</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>460</v>
+        <v>298</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="E108" t="s">
-        <v>21</v>
+        <v>299</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>297</v>
       </c>
       <c r="G108" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H108" t="s">
-        <v>15</v>
-      </c>
-      <c r="I108">
+      <c r="H108" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I108" s="8">
         <v>1</v>
       </c>
       <c r="J108" s="8" t="s">
@@ -11999,34 +12032,34 @@
       </c>
       <c r="K108" s="8" t="s">
         <v>473</v>
-      </c>
-      <c r="L108" s="8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
-        <v>5534</v>
+        <v>5347</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>469</v>
+        <v>300</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>460</v>
+        <v>302</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="E109" t="s">
-        <v>102</v>
+        <v>301</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>301</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H109" t="s">
-        <v>15</v>
-      </c>
-      <c r="I109">
+        <v>472</v>
+      </c>
+      <c r="H109" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I109" s="8">
         <v>1</v>
       </c>
       <c r="J109" s="8" t="s">
@@ -12034,34 +12067,31 @@
       </c>
       <c r="K109" s="8" t="s">
         <v>473</v>
-      </c>
-      <c r="L109" s="8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
-        <v>5534</v>
+        <v>5474</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>469</v>
+        <v>386</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>460</v>
+        <v>388</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="E110" t="s">
-        <v>86</v>
+        <v>389</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>507</v>
       </c>
       <c r="G110" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H110" t="s">
-        <v>15</v>
-      </c>
-      <c r="I110">
+      <c r="H110" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I110" s="8">
         <v>1</v>
       </c>
       <c r="J110" s="8" t="s">
@@ -12069,9 +12099,6 @@
       </c>
       <c r="K110" s="8" t="s">
         <v>473</v>
-      </c>
-      <c r="L110" s="8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
@@ -12088,7 +12115,7 @@
         <v>390</v>
       </c>
       <c r="E111" t="s">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="G111" s="8" t="s">
         <v>13</v>
@@ -12110,124 +12137,134 @@
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A112" s="12">
-        <v>5537</v>
-      </c>
-      <c r="B112" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="C112" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="D112" s="12" t="s">
-        <v>394</v>
-      </c>
-      <c r="E112" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="F112" s="12"/>
-      <c r="G112" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H112" s="12"/>
-      <c r="I112" s="12"/>
-      <c r="J112" s="12"/>
-      <c r="K112" s="12"/>
-      <c r="L112" s="12" t="s">
-        <v>467</v>
+      <c r="A112" s="8">
+        <v>5534</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="E112" t="s">
+        <v>102</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H112" t="s">
+        <v>15</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="J112" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K112" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="L112" s="8" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="8">
-        <v>5977</v>
+        <v>5534</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>469</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>395</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="G113" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="H113" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I113" s="8">
-        <v>1000</v>
+        <v>390</v>
+      </c>
+      <c r="E113" t="s">
+        <v>86</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H113" t="s">
+        <v>15</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
       </c>
       <c r="J113" s="8" t="s">
         <v>14</v>
       </c>
       <c r="K113" s="8" t="s">
         <v>473</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
-        <v>5978</v>
+        <v>5534</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>303</v>
+        <v>469</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>305</v>
+        <v>460</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="E114" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="F114" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="G114" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="H114" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I114" s="8">
-        <v>1000</v>
+        <v>390</v>
+      </c>
+      <c r="E114" t="s">
+        <v>141</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H114" t="s">
+        <v>15</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
       </c>
       <c r="J114" s="8" t="s">
         <v>14</v>
       </c>
       <c r="K114" s="8" t="s">
         <v>473</v>
+      </c>
+      <c r="L114" s="8" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
-        <v>5979</v>
+        <v>5537</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>306</v>
+        <v>391</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>308</v>
+        <v>393</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>309</v>
+        <v>394</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F115" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="G115" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="H115" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I115" s="8">
-        <v>1000</v>
+        <v>121</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H115" t="s">
+        <v>15</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
       </c>
       <c r="J115" s="8" t="s">
         <v>14</v>
@@ -12235,31 +12272,34 @@
       <c r="K115" s="8" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="116" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="20" t="s">
-        <v>502</v>
+      <c r="L115" s="8" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A116" s="8">
+        <v>5537</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="E116" t="s">
-        <v>488</v>
-      </c>
-      <c r="G116" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="H116" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I116" s="8">
-        <v>1000</v>
+        <v>394</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H116" t="s">
+        <v>15</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
       </c>
       <c r="J116" s="8" t="s">
         <v>14</v>
@@ -12267,140 +12307,162 @@
       <c r="K116" s="8" t="s">
         <v>473</v>
       </c>
+      <c r="L116" s="8" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A117" s="20" t="s">
-        <v>503</v>
+      <c r="A117" s="8">
+        <v>5537</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="E117" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="G117" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="H117" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I117" s="8">
-        <v>1000</v>
+        <v>394</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H117" t="s">
+        <v>15</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
       </c>
       <c r="J117" s="8" t="s">
         <v>14</v>
       </c>
       <c r="K117" s="8" t="s">
         <v>473</v>
+      </c>
+      <c r="L117" s="8" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="8">
-        <v>6616</v>
+        <v>5537</v>
       </c>
       <c r="B118" s="8" t="s">
-        <v>310</v>
+        <v>391</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>312</v>
+        <v>393</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>313</v>
+        <v>394</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="F118" s="8" t="s">
-        <v>311</v>
+        <v>129</v>
       </c>
       <c r="G118" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H118" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I118" s="8">
+      <c r="H118" t="s">
+        <v>15</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K118" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="L118" s="8" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A119" s="8">
+        <v>5977</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="G119" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="H119" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I119" s="8">
         <v>1000</v>
       </c>
-      <c r="J118" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K118" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A119" s="12">
-        <v>6678</v>
-      </c>
-      <c r="B119" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="C119" s="12"/>
-      <c r="D119" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="E119" s="12"/>
-      <c r="F119" s="12"/>
-      <c r="G119" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H119" s="12"/>
-      <c r="I119" s="12"/>
-      <c r="J119" s="12"/>
-      <c r="K119" s="12"/>
-      <c r="L119" s="12" t="s">
-        <v>467</v>
+      <c r="J119" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K119" s="8" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A120" s="12">
-        <v>6678</v>
-      </c>
-      <c r="B120" s="12" t="s">
-        <v>469</v>
-      </c>
-      <c r="C120" s="12"/>
-      <c r="D120" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="E120" s="12"/>
-      <c r="F120" s="12"/>
-      <c r="G120" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H120" s="12"/>
-      <c r="I120" s="12"/>
-      <c r="J120" s="12"/>
-      <c r="K120" s="12"/>
-      <c r="L120" s="12" t="s">
-        <v>467</v>
+      <c r="A120" s="8">
+        <v>5978</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="G120" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I120" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J120" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K120" s="8" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="8">
-        <v>6830</v>
+        <v>5979</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="G121" s="18" t="s">
         <v>472</v>
@@ -12418,33 +12480,30 @@
         <v>473</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A122" s="8">
-        <v>7073</v>
+    <row r="122" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="20" t="s">
+        <v>502</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>318</v>
+        <v>396</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>320</v>
+        <v>398</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="F122" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="G122" s="8" t="s">
-        <v>184</v>
+        <v>399</v>
+      </c>
+      <c r="E122" t="s">
+        <v>488</v>
+      </c>
+      <c r="G122" s="18" t="s">
+        <v>472</v>
       </c>
       <c r="H122" s="8" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="I122" s="8">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="J122" s="8" t="s">
         <v>14</v>
@@ -12454,65 +12513,82 @@
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A123" s="12">
-        <v>7128</v>
-      </c>
-      <c r="B123" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="C123" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="D123" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="E123" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="F123" s="12"/>
-      <c r="G123" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12" t="s">
-        <v>467</v>
+      <c r="A123" s="20" t="s">
+        <v>503</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="G123" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="H123" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I123" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J123" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K123" s="8" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A124" s="12">
-        <v>7170</v>
-      </c>
-      <c r="B124" s="12"/>
-      <c r="C124" s="12"/>
-      <c r="D124" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="E124" s="12"/>
-      <c r="F124" s="12"/>
-      <c r="G124" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H124" s="12"/>
-      <c r="I124" s="12"/>
-      <c r="J124" s="12"/>
-      <c r="K124" s="12"/>
-      <c r="L124" s="12" t="s">
-        <v>467</v>
+      <c r="A124" s="8">
+        <v>6616</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E124" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H124" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I124" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J124" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K124" s="8" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="12">
-        <v>7706</v>
+        <v>6678</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>469</v>
+        <v>400</v>
       </c>
       <c r="C125" s="12"/>
       <c r="D125" s="12" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="E125" s="12"/>
       <c r="F125" s="12"/>
@@ -12527,103 +12603,119 @@
         <v>467</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="20" t="s">
-        <v>409</v>
-      </c>
-      <c r="B126" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="D126" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="G126" s="8" t="s">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A126" s="12">
+        <v>6678</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="C126" s="12"/>
+      <c r="D126" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="E126" s="12"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H126" s="21"/>
+      <c r="I126" s="12"/>
+      <c r="J126" s="12"/>
+      <c r="K126" s="12"/>
+      <c r="L126" s="12" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A127" s="8">
+        <v>6830</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="E127" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="G127" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="H127" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I127" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J127" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K127" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A128" s="8">
+        <v>7073</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="G128" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="H126" s="8" t="s">
+      <c r="H128" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="I126" s="8">
-        <v>1</v>
-      </c>
-      <c r="J126" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K126" s="8" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="20" t="s">
-        <v>411</v>
-      </c>
-      <c r="B127" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="D127" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="E127" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="G127" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H127" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="I127" s="8">
-        <v>1</v>
-      </c>
-      <c r="J127" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K127" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A128" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="B128" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="C128" s="12"/>
-      <c r="D128" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="E128" s="12"/>
-      <c r="F128" s="12"/>
-      <c r="G128" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="H128" s="12"/>
-      <c r="I128" s="12"/>
-      <c r="J128" s="12"/>
-      <c r="K128" s="12"/>
-      <c r="L128" s="12" t="s">
-        <v>467</v>
+      <c r="I128" s="8">
+        <v>1</v>
+      </c>
+      <c r="J128" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K128" s="8" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A129" s="15" t="s">
-        <v>416</v>
+      <c r="A129" s="12">
+        <v>7128</v>
       </c>
       <c r="B129" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="C129" s="12"/>
+        <v>403</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>405</v>
+      </c>
       <c r="D129" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="E129" s="12"/>
+        <v>406</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>404</v>
+      </c>
       <c r="F129" s="12"/>
-      <c r="G129" s="19" t="s">
-        <v>498</v>
+      <c r="G129" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="H129" s="12"/>
       <c r="I129" s="12"/>
@@ -12634,20 +12726,18 @@
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A130" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="B130" s="12" t="s">
-        <v>422</v>
-      </c>
+      <c r="A130" s="12">
+        <v>7170</v>
+      </c>
+      <c r="B130" s="12"/>
       <c r="C130" s="12"/>
       <c r="D130" s="12" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="E130" s="12"/>
       <c r="F130" s="12"/>
-      <c r="G130" s="19" t="s">
-        <v>498</v>
+      <c r="G130" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="H130" s="12"/>
       <c r="I130" s="12"/>
@@ -12657,34 +12747,229 @@
         <v>467</v>
       </c>
     </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A131" s="8">
+        <v>7706</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H131" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I131" s="8">
+        <v>1</v>
+      </c>
+      <c r="J131" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K131" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="L131" s="8" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A132" s="8">
+        <v>7706</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H132" t="s">
+        <v>15</v>
+      </c>
+      <c r="I132" s="8">
+        <v>1</v>
+      </c>
+      <c r="J132" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K132" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="L132" s="8" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="B133" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H133" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="I133" s="8">
+        <v>1</v>
+      </c>
+      <c r="J133" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K133" s="8" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H134" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="I134" s="8">
+        <v>1</v>
+      </c>
+      <c r="J134" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K134" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A135" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="B135" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="C135" s="12"/>
+      <c r="D135" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="E135" s="12"/>
+      <c r="F135" s="12"/>
+      <c r="G135" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="H135" s="12"/>
+      <c r="I135" s="12"/>
+      <c r="J135" s="12"/>
+      <c r="K135" s="12"/>
+      <c r="L135" s="12" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A136" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="B136" s="12" t="s">
+        <v>417</v>
+      </c>
+      <c r="C136" s="12"/>
+      <c r="D136" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="E136" s="12"/>
+      <c r="F136" s="12"/>
+      <c r="G136" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="H136" s="12"/>
+      <c r="I136" s="12"/>
+      <c r="J136" s="12"/>
+      <c r="K136" s="12"/>
+      <c r="L136" s="12" t="s">
+        <v>467</v>
+      </c>
+    </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A137"/>
-      <c r="B137"/>
-      <c r="C137"/>
-      <c r="D137"/>
-      <c r="E137"/>
-      <c r="F137"/>
-      <c r="G137"/>
-      <c r="H137"/>
-      <c r="I137"/>
-      <c r="J137"/>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A138"/>
-      <c r="B138"/>
-      <c r="C138"/>
-      <c r="D138"/>
-      <c r="E138"/>
-      <c r="F138"/>
-      <c r="G138"/>
-      <c r="H138"/>
-      <c r="I138"/>
-      <c r="J138"/>
+      <c r="A137" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="C137" s="12"/>
+      <c r="D137" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="E137" s="12"/>
+      <c r="F137" s="12"/>
+      <c r="G137" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="H137" s="12"/>
+      <c r="I137" s="12"/>
+      <c r="J137" s="12"/>
+      <c r="K137" s="12"/>
+      <c r="L137" s="12" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A144"/>
+      <c r="B144"/>
+      <c r="C144"/>
+      <c r="D144"/>
+      <c r="E144"/>
+      <c r="F144"/>
+      <c r="G144"/>
+      <c r="H144"/>
+      <c r="I144"/>
+      <c r="J144"/>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A145"/>
+      <c r="B145"/>
+      <c r="C145"/>
+      <c r="D145"/>
+      <c r="E145"/>
+      <c r="F145"/>
+      <c r="G145"/>
+      <c r="H145"/>
+      <c r="I145"/>
+      <c r="J145"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L130" xr:uid="{4C99E872-61DA-4FE9-85D3-BDDE6515F002}"/>
+  <autoFilter ref="A1:L137" xr:uid="{4C99E872-61DA-4FE9-85D3-BDDE6515F002}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/mappings/parameter_mapping_final.xlsx
+++ b/mappings/parameter_mapping_final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ocean\Work\Projects\2026\ISC\Tools\Repositories\mappings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55F7FD7-F3C6-4AE3-A8A1-38886982903B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F9959C-579D-45F9-9F12-C0B0CF5145AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-45" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="wadar_isc_cas" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="missing" sheetId="10" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">mapping!$A$1:$L$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">mapping!$A$1:$L$131</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">total_mapping!$A$1:$I$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">wadar_isc_cas!$A$1:$I$80</definedName>
   </definedNames>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3919" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3811" uniqueCount="513">
   <si>
     <t>Unieke identificatie gemeten parameter</t>
   </si>
@@ -1515,9 +1515,6 @@
     <t>parameter_code</t>
   </si>
   <si>
-    <t>S</t>
-  </si>
-  <si>
     <t>TOC</t>
   </si>
   <si>
@@ -1570,6 +1567,21 @@
   </si>
   <si>
     <t>IBD</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>SNV</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> µg/L</t>
   </si>
 </sst>
 </file>
@@ -1609,7 +1621,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1631,6 +1643,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1671,7 +1689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1703,9 +1721,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1713,13 +1728,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8359,7 +8385,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C99E872-61DA-4FE9-85D3-BDDE6515F002}">
-  <dimension ref="A1:L145"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.88671875" style="8" customWidth="1"/>
@@ -8404,13 +8430,13 @@
       <c r="H1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="17" t="s">
-        <v>501</v>
+      <c r="I1" s="16" t="s">
+        <v>500</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="15" t="s">
         <v>474</v>
       </c>
       <c r="L1" s="10" t="s">
@@ -10116,7 +10142,7 @@
         <v>473</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H51" s="8" t="s">
         <v>477</v>
@@ -10288,61 +10314,54 @@
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" s="8">
+      <c r="A57" s="12">
         <v>1319</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="E57" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="G57" s="8" t="s">
+      <c r="E57" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="H57" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="I57" s="8">
-        <v>1</v>
-      </c>
-      <c r="J57" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K57" t="s">
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="19"/>
+      <c r="L57" s="12" t="s">
         <v>467</v>
-      </c>
-      <c r="L57" s="8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
-        <v>1319</v>
+        <v>1335</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>187</v>
+        <v>441</v>
       </c>
       <c r="G58" s="8" t="s">
         <v>190</v>
       </c>
       <c r="H58" t="s">
-        <v>185</v>
+        <v>503</v>
       </c>
       <c r="I58">
         <v>1</v>
@@ -10353,28 +10372,28 @@
       <c r="K58" t="s">
         <v>480</v>
       </c>
-      <c r="L58" s="8" t="s">
-        <v>490</v>
-      </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
-        <v>1319</v>
+        <v>1337</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>440</v>
+        <v>491</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>182</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>348</v>
+        <v>183</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>445</v>
+        <v>181</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>181</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H59" t="s">
         <v>185</v>
@@ -10386,33 +10405,30 @@
         <v>14</v>
       </c>
       <c r="K59" t="s">
-        <v>480</v>
-      </c>
-      <c r="L59" s="8" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>442</v>
+        <v>495</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>444</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H60" t="s">
-        <v>504</v>
+        <v>185</v>
       </c>
       <c r="I60">
         <v>1</v>
@@ -10421,30 +10437,30 @@
         <v>14</v>
       </c>
       <c r="K60" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H61" t="s">
         <v>185</v>
@@ -10456,27 +10472,27 @@
         <v>14</v>
       </c>
       <c r="K61" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>444</v>
+        <v>492</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>446</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H62" t="s">
         <v>185</v>
@@ -10488,129 +10504,127 @@
         <v>14</v>
       </c>
       <c r="K62" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63" s="8">
-        <v>1339</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="F63" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="H63" t="s">
+      <c r="A63" s="20">
+        <v>1345</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="D63" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>473</v>
+      </c>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20" t="s">
+        <v>499</v>
+      </c>
+      <c r="H63" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="I63">
-        <v>1</v>
-      </c>
-      <c r="J63" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K63" t="s">
-        <v>480</v>
+      <c r="I63" s="20">
+        <v>0.1</v>
+      </c>
+      <c r="J63" s="20" t="s">
+        <v>447</v>
+      </c>
+      <c r="K63" s="21" t="s">
+        <v>482</v>
+      </c>
+      <c r="L63" s="20" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
-        <v>1340</v>
+        <v>1350</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>446</v>
+        <v>335</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>450</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>445</v>
+        <v>357</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>449</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H64" t="s">
         <v>185</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="8">
         <v>1</v>
       </c>
       <c r="J64" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K64" t="s">
-        <v>480</v>
+      <c r="K64" s="8" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>335</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>473</v>
+        <v>357</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>449</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>500</v>
+        <v>184</v>
       </c>
       <c r="H65" t="s">
         <v>185</v>
       </c>
       <c r="I65" s="8">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="K65" t="s">
-        <v>482</v>
+        <v>14</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
-        <v>1350</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>335</v>
+        <v>1361</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>449</v>
+        <v>358</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>451</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H66" t="s">
-        <v>185</v>
+        <v>13</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="I66" s="8">
         <v>1</v>
@@ -10619,30 +10633,27 @@
         <v>14</v>
       </c>
       <c r="K66" s="8" t="s">
-        <v>506</v>
+        <v>481</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
-        <v>1350</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>335</v>
+        <v>1368</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>449</v>
+        <v>359</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>453</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H67" t="s">
-        <v>185</v>
+        <v>13</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="I67" s="8">
         <v>1</v>
@@ -10651,32 +10662,38 @@
         <v>14</v>
       </c>
       <c r="K67" s="8" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A68" s="8">
-        <v>1361</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H68" s="8" t="s">
+      <c r="A68">
+        <v>1369</v>
+      </c>
+      <c r="B68" t="s">
+        <v>191</v>
+      </c>
+      <c r="C68" t="s">
+        <v>193</v>
+      </c>
+      <c r="D68" t="s">
+        <v>194</v>
+      </c>
+      <c r="E68" t="s">
+        <v>192</v>
+      </c>
+      <c r="F68" t="s">
+        <v>192</v>
+      </c>
+      <c r="G68" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="8">
         <v>1</v>
       </c>
-      <c r="J68" s="8" t="s">
+      <c r="J68" t="s">
         <v>14</v>
       </c>
       <c r="K68" s="8" t="s">
@@ -10684,28 +10701,34 @@
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A69" s="8">
-        <v>1368</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H69" s="8" t="s">
+      <c r="A69">
+        <v>1379</v>
+      </c>
+      <c r="B69" t="s">
+        <v>191</v>
+      </c>
+      <c r="C69" t="s">
+        <v>463</v>
+      </c>
+      <c r="D69" t="s">
+        <v>195</v>
+      </c>
+      <c r="E69" t="s">
+        <v>464</v>
+      </c>
+      <c r="F69" t="s">
+        <v>464</v>
+      </c>
+      <c r="G69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="8">
         <v>1</v>
       </c>
-      <c r="J69" s="8" t="s">
+      <c r="J69" t="s">
         <v>14</v>
       </c>
       <c r="K69" s="8" t="s">
@@ -10713,34 +10736,34 @@
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A70">
-        <v>1369</v>
-      </c>
-      <c r="B70" t="s">
-        <v>191</v>
-      </c>
-      <c r="C70" t="s">
-        <v>193</v>
-      </c>
-      <c r="D70" t="s">
-        <v>194</v>
-      </c>
-      <c r="E70" t="s">
-        <v>192</v>
-      </c>
-      <c r="F70" t="s">
-        <v>192</v>
-      </c>
-      <c r="G70" t="s">
-        <v>13</v>
-      </c>
-      <c r="H70" t="s">
+      <c r="A70" s="8">
+        <v>1382</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="8">
         <v>1</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J70" s="8" t="s">
         <v>14</v>
       </c>
       <c r="K70" s="8" t="s">
@@ -10748,34 +10771,31 @@
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A71">
-        <v>1379</v>
-      </c>
-      <c r="B71" t="s">
-        <v>191</v>
-      </c>
-      <c r="C71" t="s">
-        <v>463</v>
-      </c>
-      <c r="D71" t="s">
-        <v>195</v>
-      </c>
-      <c r="E71" t="s">
-        <v>464</v>
-      </c>
-      <c r="F71" t="s">
-        <v>464</v>
-      </c>
-      <c r="G71" t="s">
-        <v>13</v>
-      </c>
-      <c r="H71" t="s">
+      <c r="A71" s="8">
+        <v>1383</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="8">
         <v>1</v>
       </c>
-      <c r="J71" t="s">
+      <c r="J71" s="8" t="s">
         <v>14</v>
       </c>
       <c r="K71" s="8" t="s">
@@ -10784,22 +10804,16 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
-        <v>1382</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>196</v>
+        <v>1385</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>198</v>
+        <v>458</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>199</v>
+        <v>362</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>197</v>
+        <v>457</v>
       </c>
       <c r="G72" s="8" t="s">
         <v>13</v>
@@ -10819,19 +10833,22 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="8">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>497</v>
+        <v>200</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>456</v>
+        <v>202</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>361</v>
+        <v>203</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>455</v>
+        <v>201</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>201</v>
       </c>
       <c r="G73" s="8" t="s">
         <v>13</v>
@@ -10851,16 +10868,22 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="8">
-        <v>1385</v>
+        <v>1387</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>204</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>458</v>
+        <v>206</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>362</v>
+        <v>207</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>457</v>
+        <v>205</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>205</v>
       </c>
       <c r="G74" s="8" t="s">
         <v>13</v>
@@ -10880,22 +10903,22 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G75" s="8" t="s">
         <v>13</v>
@@ -10915,22 +10938,22 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="8">
-        <v>1387</v>
+        <v>1392</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="G76" s="8" t="s">
         <v>13</v>
@@ -10950,28 +10973,28 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="8">
-        <v>1388</v>
+        <v>1433</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>13</v>
+        <v>220</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="I77" s="8">
         <v>1</v>
@@ -10979,28 +11002,28 @@
       <c r="J77" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K77" s="8" t="s">
-        <v>481</v>
+      <c r="K77" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="8">
-        <v>1392</v>
+        <v>1439</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="G78" s="8" t="s">
         <v>13</v>
@@ -11015,33 +11038,33 @@
         <v>14</v>
       </c>
       <c r="K78" s="8" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="8">
-        <v>1433</v>
+        <v>1458</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>220</v>
+        <v>13</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="I79" s="8">
         <v>1</v>
@@ -11049,28 +11072,28 @@
       <c r="J79" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K79" t="s">
-        <v>483</v>
+      <c r="K79" s="8" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="8">
-        <v>1439</v>
+        <v>1464</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="G80" s="8" t="s">
         <v>13</v>
@@ -11090,22 +11113,22 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
-        <v>1458</v>
+        <v>1517</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="G81" s="8" t="s">
         <v>13</v>
@@ -11125,28 +11148,25 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
-        <v>1464</v>
+        <v>1551</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>229</v>
+        <v>363</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>231</v>
+        <v>365</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>232</v>
+        <v>366</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>230</v>
+        <v>485</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="I82" s="8">
         <v>1</v>
@@ -11154,34 +11174,31 @@
       <c r="J82" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K82" s="8" t="s">
-        <v>473</v>
+      <c r="K82" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="8">
-        <v>1517</v>
+        <v>1551</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>233</v>
+        <v>363</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>235</v>
+        <v>365</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>236</v>
+        <v>366</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="F83" s="8" t="s">
-        <v>234</v>
+        <v>485</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="I83" s="8">
         <v>1</v>
@@ -11190,30 +11207,33 @@
         <v>14</v>
       </c>
       <c r="K83" s="8" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="8">
-        <v>1551</v>
+        <v>1629</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>363</v>
+        <v>237</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>365</v>
+        <v>239</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>366</v>
+        <v>240</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>485</v>
+        <v>238</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>238</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="I84" s="8">
         <v>1</v>
@@ -11221,31 +11241,34 @@
       <c r="J84" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K84" t="s">
-        <v>467</v>
+      <c r="K84" s="8" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="8">
-        <v>1551</v>
+        <v>1630</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>363</v>
+        <v>241</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>365</v>
+        <v>243</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>366</v>
+        <v>244</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>485</v>
+        <v>242</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>242</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>185</v>
+        <v>15</v>
       </c>
       <c r="I85" s="8">
         <v>1</v>
@@ -11254,27 +11277,27 @@
         <v>14</v>
       </c>
       <c r="K85" s="8" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="8">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="G86" s="8" t="s">
         <v>13</v>
@@ -11294,22 +11317,22 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
-        <v>1630</v>
+        <v>1688</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="G87" s="8" t="s">
         <v>13</v>
@@ -11328,58 +11351,48 @@
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A88" s="8">
-        <v>1652</v>
-      </c>
-      <c r="B88" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="G88" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H88" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I88" s="8">
-        <v>1</v>
-      </c>
-      <c r="J88" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K88" s="8" t="s">
-        <v>473</v>
+      <c r="A88" s="12">
+        <v>1743</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H88" s="12"/>
+      <c r="I88" s="12"/>
+      <c r="J88" s="12"/>
+      <c r="K88" s="12"/>
+      <c r="L88" s="12" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="8">
-        <v>1688</v>
+        <v>1774</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>249</v>
+        <v>371</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>251</v>
+        <v>373</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="F89" s="8" t="s">
-        <v>250</v>
+        <v>374</v>
+      </c>
+      <c r="E89" t="s">
+        <v>242</v>
       </c>
       <c r="G89" s="8" t="s">
         <v>13</v>
@@ -11396,33 +11409,43 @@
       <c r="K89" s="8" t="s">
         <v>473</v>
       </c>
+      <c r="L89" s="8" t="s">
+        <v>508</v>
+      </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A90" s="12">
-        <v>1743</v>
-      </c>
-      <c r="B90" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="C90" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="D90" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="E90" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="F90" s="12"/>
-      <c r="G90" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H90" s="12"/>
-      <c r="I90" s="12"/>
-      <c r="J90" s="12"/>
-      <c r="K90" s="12"/>
-      <c r="L90" s="12" t="s">
-        <v>467</v>
+      <c r="A90" s="8">
+        <v>1774</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" s="8">
+        <v>1</v>
+      </c>
+      <c r="J90" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K90" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="L90" s="8" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
@@ -11439,7 +11462,7 @@
         <v>374</v>
       </c>
       <c r="E91" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G91" s="8" t="s">
         <v>13</v>
@@ -11457,24 +11480,27 @@
         <v>473</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="8">
-        <v>1774</v>
+        <v>1877</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>371</v>
+        <v>252</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>373</v>
+        <v>254</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>374</v>
+        <v>254</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>169</v>
+        <v>253</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="G92" s="8" t="s">
         <v>13</v>
@@ -11491,25 +11517,25 @@
       <c r="K92" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="L92" s="8" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="8">
-        <v>1774</v>
+        <v>1888</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>373</v>
+        <v>255</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>257</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="E93" t="s">
-        <v>238</v>
+        <v>258</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="G93" s="8" t="s">
         <v>13</v>
@@ -11526,63 +11552,53 @@
       <c r="K93" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="L93" s="8" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="8">
-        <v>1877</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="G94" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H94" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I94" s="8">
-        <v>1</v>
-      </c>
-      <c r="J94" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K94" s="8" t="s">
-        <v>473</v>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A94" s="12">
+        <v>1920</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="C94" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H94" s="12"/>
+      <c r="I94" s="12"/>
+      <c r="J94" s="12"/>
+      <c r="K94" s="12"/>
+      <c r="L94" s="12" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="8">
-        <v>1888</v>
+        <v>1935</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="C95" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>261</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G95" s="8" t="s">
         <v>13</v>
@@ -11600,21 +11616,21 @@
         <v>473</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="12">
-        <v>1920</v>
+        <v>1955</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F96" s="12"/>
       <c r="G96" s="12" t="s">
@@ -11629,123 +11645,130 @@
       </c>
     </row>
     <row r="97" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="8">
-        <v>1935</v>
-      </c>
-      <c r="B97" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="D97" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="F97" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="G97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H97" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I97" s="8">
-        <v>1</v>
-      </c>
-      <c r="J97" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K97" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="12">
-        <v>1955</v>
-      </c>
-      <c r="B98" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="C98" s="14" t="s">
-        <v>381</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="E98" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="F98" s="12"/>
-      <c r="G98" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H98" s="12"/>
-      <c r="I98" s="12"/>
-      <c r="J98" s="12"/>
-      <c r="K98" s="12"/>
-      <c r="L98" s="12" t="s">
+      <c r="A97" s="12">
+        <v>1958</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="F97" s="12"/>
+      <c r="G97" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H97" s="12"/>
+      <c r="I97" s="12"/>
+      <c r="J97" s="12"/>
+      <c r="K97" s="12"/>
+      <c r="L97" s="12" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="12">
-        <v>1958</v>
-      </c>
-      <c r="B99" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="C99" s="14" t="s">
-        <v>385</v>
-      </c>
-      <c r="D99" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="E99" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="F99" s="12"/>
-      <c r="G99" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H99" s="12"/>
-      <c r="I99" s="12"/>
-      <c r="J99" s="12"/>
-      <c r="K99" s="12"/>
-      <c r="L99" s="12" t="s">
-        <v>467</v>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98" s="8">
+        <v>1959</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" s="8">
+        <v>1</v>
+      </c>
+      <c r="J98" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K98" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99" s="8">
+        <v>2028</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I99" s="8">
+        <v>1</v>
+      </c>
+      <c r="J99" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K99" s="8" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
-        <v>1959</v>
+        <v>2879</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="C100" s="9" t="s">
-        <v>265</v>
+        <v>271</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="G100" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>15</v>
+        <v>275</v>
       </c>
       <c r="I100" s="8">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="J100" s="8" t="s">
         <v>14</v>
@@ -11754,24 +11777,24 @@
         <v>473</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="8">
-        <v>2028</v>
+        <v>2911</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>267</v>
+        <v>494</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="G101" s="8" t="s">
         <v>13</v>
@@ -11791,31 +11814,31 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="8">
-        <v>2879</v>
+        <v>2912</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="E102" s="8" t="s">
-        <v>272</v>
+        <v>283</v>
+      </c>
+      <c r="E102" s="9" t="s">
+        <v>281</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="G102" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>275</v>
+        <v>15</v>
       </c>
       <c r="I102" s="8">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="J102" s="8" t="s">
         <v>14</v>
@@ -11824,24 +11847,24 @@
         <v>473</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="8">
-        <v>2911</v>
+        <v>2915</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>495</v>
+        <v>284</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="G103" s="8" t="s">
         <v>13</v>
@@ -11861,22 +11884,22 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="8">
-        <v>2912</v>
+        <v>2916</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="E104" s="9" t="s">
-        <v>281</v>
+        <v>291</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>289</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="G104" s="8" t="s">
         <v>13</v>
@@ -11896,22 +11919,22 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
-        <v>2915</v>
+        <v>2919</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="G105" s="8" t="s">
         <v>13</v>
@@ -11931,22 +11954,22 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="8">
-        <v>2916</v>
+        <v>2920</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="G106" s="8" t="s">
         <v>13</v>
@@ -11966,25 +11989,25 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="8">
-        <v>2919</v>
+        <v>5347</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>13</v>
+        <v>472</v>
       </c>
       <c r="H107" s="8" t="s">
         <v>15</v>
@@ -12001,22 +12024,19 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="8">
-        <v>2920</v>
+        <v>5474</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>296</v>
+        <v>386</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>298</v>
+        <v>388</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>299</v>
+        <v>389</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="F108" s="8" t="s">
-        <v>297</v>
+        <v>506</v>
       </c>
       <c r="G108" s="8" t="s">
         <v>13</v>
@@ -12036,30 +12056,27 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="8">
-        <v>5347</v>
+        <v>5534</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>300</v>
+        <v>469</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>302</v>
+        <v>460</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="E109" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="F109" s="8" t="s">
-        <v>301</v>
+        <v>390</v>
+      </c>
+      <c r="E109" t="s">
+        <v>21</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="H109" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I109" s="8">
+        <v>13</v>
+      </c>
+      <c r="H109" t="s">
+        <v>15</v>
+      </c>
+      <c r="I109">
         <v>1</v>
       </c>
       <c r="J109" s="8" t="s">
@@ -12067,31 +12084,34 @@
       </c>
       <c r="K109" s="8" t="s">
         <v>473</v>
+      </c>
+      <c r="L109" s="8" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="8">
-        <v>5474</v>
+        <v>5534</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>386</v>
+        <v>469</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>388</v>
+        <v>460</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="E110" s="8" t="s">
-        <v>507</v>
+        <v>390</v>
+      </c>
+      <c r="E110" t="s">
+        <v>102</v>
       </c>
       <c r="G110" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H110" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I110" s="8">
+      <c r="H110" t="s">
+        <v>15</v>
+      </c>
+      <c r="I110">
         <v>1</v>
       </c>
       <c r="J110" s="8" t="s">
@@ -12099,6 +12119,9 @@
       </c>
       <c r="K110" s="8" t="s">
         <v>473</v>
+      </c>
+      <c r="L110" s="8" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
@@ -12115,7 +12138,7 @@
         <v>390</v>
       </c>
       <c r="E111" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="G111" s="8" t="s">
         <v>13</v>
@@ -12133,7 +12156,7 @@
         <v>473</v>
       </c>
       <c r="L111" s="8" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
@@ -12150,7 +12173,7 @@
         <v>390</v>
       </c>
       <c r="E112" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="G112" s="8" t="s">
         <v>13</v>
@@ -12168,138 +12191,128 @@
         <v>473</v>
       </c>
       <c r="L112" s="8" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A113" s="8">
-        <v>5534</v>
-      </c>
-      <c r="B113" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="D113" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="E113" t="s">
-        <v>86</v>
-      </c>
-      <c r="G113" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H113" t="s">
-        <v>15</v>
-      </c>
-      <c r="I113">
-        <v>1</v>
-      </c>
-      <c r="J113" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K113" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="L113" s="8" t="s">
-        <v>490</v>
+      <c r="A113" s="12">
+        <v>5537</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="E113" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="F113" s="12"/>
+      <c r="G113" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H113" s="12"/>
+      <c r="I113" s="12"/>
+      <c r="J113" s="12"/>
+      <c r="K113" s="12"/>
+      <c r="L113" s="12" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="8">
-        <v>5534</v>
-      </c>
-      <c r="B114" s="8" t="s">
-        <v>469</v>
+        <v>5977</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="E114" t="s">
-        <v>141</v>
-      </c>
-      <c r="G114" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H114" t="s">
-        <v>15</v>
-      </c>
-      <c r="I114">
-        <v>1</v>
+        <v>395</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="G114" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="H114" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I114" s="8">
+        <v>1000</v>
       </c>
       <c r="J114" s="8" t="s">
         <v>14</v>
       </c>
       <c r="K114" s="8" t="s">
         <v>473</v>
-      </c>
-      <c r="L114" s="8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="8">
-        <v>5537</v>
+        <v>5978</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>391</v>
+        <v>303</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>393</v>
+        <v>305</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>394</v>
+        <v>304</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G115" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H115" t="s">
-        <v>15</v>
-      </c>
-      <c r="I115">
-        <v>1</v>
+        <v>304</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="G115" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="H115" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I115" s="8">
+        <v>1000</v>
       </c>
       <c r="J115" s="8" t="s">
         <v>14</v>
       </c>
       <c r="K115" s="8" t="s">
         <v>473</v>
-      </c>
-      <c r="L115" s="8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="8">
-        <v>5537</v>
+        <v>5979</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>391</v>
+        <v>306</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>393</v>
+        <v>308</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>394</v>
+        <v>309</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="G116" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H116" t="s">
-        <v>15</v>
-      </c>
-      <c r="I116">
-        <v>1</v>
+        <v>307</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="G116" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="H116" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I116" s="8">
+        <v>1000</v>
       </c>
       <c r="J116" s="8" t="s">
         <v>14</v>
@@ -12307,95 +12320,100 @@
       <c r="K116" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="L116" s="8" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A117" s="8">
-        <v>5537</v>
-      </c>
-      <c r="B117" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="D117" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="E117" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="G117" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H117" t="s">
-        <v>15</v>
-      </c>
-      <c r="I117">
-        <v>1</v>
-      </c>
-      <c r="J117" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K117" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="L117" s="8" t="s">
-        <v>490</v>
+    </row>
+    <row r="117" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="B117" s="23" t="s">
+        <v>396</v>
+      </c>
+      <c r="C117" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="D117" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="E117" s="24" t="s">
+        <v>488</v>
+      </c>
+      <c r="F117" s="23"/>
+      <c r="G117" s="25" t="s">
+        <v>472</v>
+      </c>
+      <c r="H117" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I117" s="23">
+        <v>1000</v>
+      </c>
+      <c r="J117" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="K117" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="L117" s="23" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A118" s="8">
-        <v>5537</v>
-      </c>
-      <c r="B118" s="8" t="s">
-        <v>391</v>
-      </c>
-      <c r="C118" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="D118" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="G118" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H118" t="s">
-        <v>15</v>
-      </c>
-      <c r="I118">
-        <v>1</v>
-      </c>
-      <c r="J118" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K118" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="L118" s="8" t="s">
-        <v>490</v>
+      <c r="A118" s="22" t="s">
+        <v>502</v>
+      </c>
+      <c r="B118" s="23" t="s">
+        <v>396</v>
+      </c>
+      <c r="C118" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="D118" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="E118" s="26" t="s">
+        <v>487</v>
+      </c>
+      <c r="F118" s="23"/>
+      <c r="G118" s="25" t="s">
+        <v>472</v>
+      </c>
+      <c r="H118" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I118" s="23">
+        <v>1000</v>
+      </c>
+      <c r="J118" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="K118" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="L118" s="23" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="8">
-        <v>5977</v>
+        <v>6616</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>310</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>462</v>
+        <v>312</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>395</v>
+        <v>313</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="G119" s="18" t="s">
-        <v>472</v>
+        <v>311</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="H119" s="8" t="s">
         <v>15</v>
@@ -12411,92 +12429,73 @@
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A120" s="8">
-        <v>5978</v>
-      </c>
-      <c r="B120" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="C120" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="D120" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="E120" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="F120" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="G120" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="H120" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I120" s="8">
-        <v>1000</v>
-      </c>
-      <c r="J120" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K120" s="8" t="s">
-        <v>473</v>
+      <c r="A120" s="12">
+        <v>6678</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="C120" s="12"/>
+      <c r="D120" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="E120" s="12"/>
+      <c r="F120" s="12"/>
+      <c r="G120" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H120" s="12"/>
+      <c r="I120" s="12"/>
+      <c r="J120" s="12"/>
+      <c r="K120" s="12"/>
+      <c r="L120" s="12" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A121" s="8">
-        <v>5979</v>
-      </c>
-      <c r="B121" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="D121" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F121" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="G121" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="H121" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I121" s="8">
-        <v>1000</v>
-      </c>
-      <c r="J121" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K121" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="20" t="s">
-        <v>502</v>
+      <c r="A121" s="12">
+        <v>6678</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="C121" s="12"/>
+      <c r="D121" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="E121" s="12"/>
+      <c r="F121" s="12"/>
+      <c r="G121" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H121" s="19"/>
+      <c r="I121" s="12"/>
+      <c r="J121" s="12"/>
+      <c r="K121" s="12"/>
+      <c r="L121" s="12" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A122" s="8">
+        <v>6830</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>396</v>
+        <v>314</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>398</v>
+        <v>316</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="E122" t="s">
-        <v>488</v>
-      </c>
-      <c r="G122" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="G122" s="17" t="s">
         <v>472</v>
       </c>
       <c r="H122" s="8" t="s">
@@ -12513,29 +12512,32 @@
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A123" s="20" t="s">
-        <v>503</v>
+      <c r="A123" s="8">
+        <v>7073</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>396</v>
+        <v>318</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>398</v>
+        <v>320</v>
       </c>
       <c r="D123" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="E123" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="G123" s="18" t="s">
-        <v>472</v>
+        <v>321</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>184</v>
       </c>
       <c r="H123" s="8" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="I123" s="8">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="J123" s="8" t="s">
         <v>14</v>
@@ -12545,50 +12547,41 @@
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A124" s="8">
-        <v>6616</v>
-      </c>
-      <c r="B124" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C124" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="D124" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="E124" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="F124" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="G124" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H124" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I124" s="8">
-        <v>1000</v>
-      </c>
-      <c r="J124" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K124" s="8" t="s">
-        <v>473</v>
+      <c r="A124" s="12">
+        <v>7128</v>
+      </c>
+      <c r="B124" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="E124" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="F124" s="12"/>
+      <c r="G124" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="12" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="12">
-        <v>6678</v>
-      </c>
-      <c r="B125" s="12" t="s">
-        <v>400</v>
-      </c>
+        <v>7170</v>
+      </c>
+      <c r="B125" s="12"/>
       <c r="C125" s="12"/>
       <c r="D125" s="12" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="E125" s="12"/>
       <c r="F125" s="12"/>
@@ -12605,21 +12598,21 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="12">
-        <v>6678</v>
+        <v>7706</v>
       </c>
       <c r="B126" s="12" t="s">
         <v>469</v>
       </c>
       <c r="C126" s="12"/>
       <c r="D126" s="12" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E126" s="12"/>
       <c r="F126" s="12"/>
       <c r="G126" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H126" s="21"/>
+        <v>512</v>
+      </c>
+      <c r="H126" s="12"/>
       <c r="I126" s="12"/>
       <c r="J126" s="12"/>
       <c r="K126" s="12"/>
@@ -12627,59 +12620,47 @@
         <v>467</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A127" s="8">
-        <v>6830</v>
+    <row r="127" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="18" t="s">
+        <v>409</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>317</v>
+        <v>410</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="F127" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="G127" s="18" t="s">
-        <v>472</v>
+        <v>504</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>184</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="I127" s="8">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="J127" s="8" t="s">
         <v>14</v>
       </c>
       <c r="K127" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A128" s="8">
-        <v>7073</v>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="18" t="s">
+        <v>411</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="C128" s="8" t="s">
-        <v>320</v>
+        <v>469</v>
       </c>
       <c r="D128" s="8" t="s">
-        <v>321</v>
+        <v>412</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="F128" s="8" t="s">
-        <v>319</v>
+        <v>490</v>
       </c>
       <c r="G128" s="8" t="s">
         <v>184</v>
@@ -12698,275 +12679,103 @@
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A129" s="12">
-        <v>7128</v>
-      </c>
-      <c r="B129" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="C129" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="D129" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="E129" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="F129" s="12"/>
-      <c r="G129" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H129" s="12"/>
-      <c r="I129" s="12"/>
-      <c r="J129" s="12"/>
-      <c r="K129" s="12"/>
-      <c r="L129" s="12" t="s">
-        <v>467</v>
+      <c r="A129" s="22" t="s">
+        <v>507</v>
+      </c>
+      <c r="B129" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="C129" s="23"/>
+      <c r="D129" s="23" t="s">
+        <v>415</v>
+      </c>
+      <c r="E129" s="23"/>
+      <c r="F129" s="23"/>
+      <c r="G129" s="25" t="s">
+        <v>497</v>
+      </c>
+      <c r="H129" s="23"/>
+      <c r="I129" s="23"/>
+      <c r="J129" s="23"/>
+      <c r="K129" s="23"/>
+      <c r="L129" s="23" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A130" s="12">
-        <v>7170</v>
-      </c>
-      <c r="B130" s="12"/>
-      <c r="C130" s="12"/>
-      <c r="D130" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="E130" s="12"/>
-      <c r="F130" s="12"/>
-      <c r="G130" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H130" s="12"/>
-      <c r="I130" s="12"/>
-      <c r="J130" s="12"/>
-      <c r="K130" s="12"/>
-      <c r="L130" s="12" t="s">
-        <v>467</v>
+      <c r="A130" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="B130" s="23" t="s">
+        <v>417</v>
+      </c>
+      <c r="C130" s="23"/>
+      <c r="D130" s="23" t="s">
+        <v>418</v>
+      </c>
+      <c r="E130" s="23"/>
+      <c r="F130" s="23"/>
+      <c r="G130" s="25" t="s">
+        <v>497</v>
+      </c>
+      <c r="H130" s="23"/>
+      <c r="I130" s="23"/>
+      <c r="J130" s="23"/>
+      <c r="K130" s="23"/>
+      <c r="L130" s="23" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A131" s="8">
-        <v>7706</v>
-      </c>
-      <c r="B131" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="D131" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="E131" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="G131" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H131" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I131" s="8">
-        <v>1</v>
-      </c>
-      <c r="J131" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K131" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="L131" s="8" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A132" s="8">
-        <v>7706</v>
-      </c>
-      <c r="B132" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="D132" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G132" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H132" t="s">
-        <v>15</v>
-      </c>
-      <c r="I132" s="8">
-        <v>1</v>
-      </c>
-      <c r="J132" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K132" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="L132" s="8" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="20" t="s">
-        <v>409</v>
-      </c>
-      <c r="B133" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="D133" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="E133" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="G133" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H133" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="I133" s="8">
-        <v>1</v>
-      </c>
-      <c r="J133" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K133" s="8" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="20" t="s">
-        <v>411</v>
-      </c>
-      <c r="B134" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="D134" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="E134" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="G134" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H134" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="I134" s="8">
-        <v>1</v>
-      </c>
-      <c r="J134" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K134" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A135" s="15" t="s">
-        <v>508</v>
-      </c>
-      <c r="B135" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="C135" s="12"/>
-      <c r="D135" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="E135" s="12"/>
-      <c r="F135" s="12"/>
-      <c r="G135" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="H135" s="12"/>
-      <c r="I135" s="12"/>
-      <c r="J135" s="12"/>
-      <c r="K135" s="12"/>
-      <c r="L135" s="12" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A136" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="B136" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="C136" s="12"/>
-      <c r="D136" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="E136" s="12"/>
-      <c r="F136" s="12"/>
-      <c r="G136" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="H136" s="12"/>
-      <c r="I136" s="12"/>
-      <c r="J136" s="12"/>
-      <c r="K136" s="12"/>
-      <c r="L136" s="12" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A137" s="15" t="s">
+      <c r="A131" s="22" t="s">
         <v>420</v>
       </c>
-      <c r="B137" s="12" t="s">
+      <c r="B131" s="23" t="s">
         <v>422</v>
       </c>
-      <c r="C137" s="12"/>
-      <c r="D137" s="12" t="s">
+      <c r="C131" s="23"/>
+      <c r="D131" s="23" t="s">
         <v>423</v>
       </c>
-      <c r="E137" s="12"/>
-      <c r="F137" s="12"/>
-      <c r="G137" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="H137" s="12"/>
-      <c r="I137" s="12"/>
-      <c r="J137" s="12"/>
-      <c r="K137" s="12"/>
-      <c r="L137" s="12" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A144"/>
-      <c r="B144"/>
-      <c r="C144"/>
-      <c r="D144"/>
-      <c r="E144"/>
-      <c r="F144"/>
-      <c r="G144"/>
-      <c r="H144"/>
-      <c r="I144"/>
-      <c r="J144"/>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A145"/>
-      <c r="B145"/>
-      <c r="C145"/>
-      <c r="D145"/>
-      <c r="E145"/>
-      <c r="F145"/>
-      <c r="G145"/>
-      <c r="H145"/>
-      <c r="I145"/>
-      <c r="J145"/>
+      <c r="E131" s="23"/>
+      <c r="F131" s="23"/>
+      <c r="G131" s="25" t="s">
+        <v>497</v>
+      </c>
+      <c r="H131" s="23"/>
+      <c r="I131" s="23"/>
+      <c r="J131" s="23"/>
+      <c r="K131" s="23"/>
+      <c r="L131" s="23" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A138"/>
+      <c r="B138"/>
+      <c r="C138"/>
+      <c r="D138"/>
+      <c r="E138"/>
+      <c r="F138"/>
+      <c r="G138"/>
+      <c r="H138"/>
+      <c r="I138"/>
+      <c r="J138"/>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A139"/>
+      <c r="B139"/>
+      <c r="C139"/>
+      <c r="D139"/>
+      <c r="E139"/>
+      <c r="F139"/>
+      <c r="G139"/>
+      <c r="H139"/>
+      <c r="I139"/>
+      <c r="J139"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L137" xr:uid="{4C99E872-61DA-4FE9-85D3-BDDE6515F002}"/>
+  <autoFilter ref="A1:L131" xr:uid="{4C99E872-61DA-4FE9-85D3-BDDE6515F002}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12975,7 +12784,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F3409E8-107C-4F76-A795-EEC67CFABDCC}">
-  <dimension ref="A1:L117"/>
+  <dimension ref="A1:L118"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.88671875" style="8" customWidth="1"/>
@@ -13020,13 +12829,13 @@
       <c r="H1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="17" t="s">
-        <v>501</v>
+      <c r="I1" s="16" t="s">
+        <v>500</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="15" t="s">
         <v>474</v>
       </c>
       <c r="L1" s="10" t="s">
@@ -13974,27 +13783,27 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G29" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="8">
@@ -14009,22 +13818,22 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>13</v>
@@ -14044,22 +13853,22 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G31" s="8" t="s">
         <v>13</v>
@@ -14079,22 +13888,22 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G32" s="8" t="s">
         <v>13</v>
@@ -14114,22 +13923,22 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>13</v>
@@ -14149,22 +13958,22 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G34" s="8" t="s">
         <v>13</v>
@@ -14184,22 +13993,22 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G35" s="8" t="s">
         <v>13</v>
@@ -14219,22 +14028,22 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G36" s="8" t="s">
         <v>13</v>
@@ -14254,22 +14063,22 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
-        <v>1235</v>
+        <v>1208</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>13</v>
@@ -14289,22 +14098,22 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
-        <v>1263</v>
+        <v>1235</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>13</v>
@@ -14324,22 +14133,22 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
-        <v>1269</v>
+        <v>1263</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>13</v>
@@ -14359,22 +14168,22 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G40" s="8" t="s">
         <v>13</v>
@@ -14394,22 +14203,22 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G41" s="8" t="s">
         <v>13</v>
@@ -14429,22 +14238,22 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
-        <v>1283</v>
+        <v>1276</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G42" s="8" t="s">
         <v>13</v>
@@ -14464,22 +14273,22 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>13</v>
@@ -14499,22 +14308,22 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G44" s="8" t="s">
         <v>13</v>
@@ -14534,31 +14343,34 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
-        <v>1301</v>
+        <v>1289</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>335</v>
+        <v>176</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>428</v>
+        <v>178</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>336</v>
+        <v>179</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>473</v>
+        <v>177</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>177</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>337</v>
+        <v>13</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>475</v>
+        <v>15</v>
       </c>
       <c r="I45" s="8">
         <v>1</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>427</v>
+        <v>14</v>
       </c>
       <c r="K45" s="8" t="s">
         <v>473</v>
@@ -14566,31 +14378,31 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>335</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>473</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I46" s="8">
         <v>1</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>338</v>
+        <v>427</v>
       </c>
       <c r="K46" s="8" t="s">
         <v>473</v>
@@ -14598,83 +14410,83 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>335</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>473</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>499</v>
+        <v>339</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="I47" s="8">
-        <v>11.1</v>
+        <v>1</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>430</v>
+        <v>338</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>335</v>
       </c>
       <c r="C48" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="I48" s="8">
+        <v>11.1</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="8">
+        <v>1305</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D49" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E49" s="8" t="s">
         <v>432</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="I48" s="8">
-        <v>1</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A49" s="8">
-        <v>1311</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>435</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>434</v>
       </c>
       <c r="G49" s="8" t="s">
         <v>184</v>
@@ -14692,7 +14504,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>1311</v>
       </c>
@@ -14709,135 +14521,135 @@
         <v>434</v>
       </c>
       <c r="G50" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="I50" s="8">
+        <v>1</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="8">
+        <v>1311</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="G51" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="H50" s="8" t="s">
+      <c r="H51" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="I50" s="8">
-        <v>1</v>
-      </c>
-      <c r="J50" s="8" t="s">
+      <c r="I51" s="8">
+        <v>1</v>
+      </c>
+      <c r="J51" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="K50" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A51" s="8">
+      <c r="K51" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="8">
         <v>1313</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B52" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C52" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D52" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E52" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="G51" s="8" t="s">
+      <c r="G52" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H52" t="s">
         <v>185</v>
       </c>
-      <c r="I51">
-        <v>1</v>
-      </c>
-      <c r="J51" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A52" s="8">
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="8">
         <v>1335</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B53" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C53" s="11" t="s">
         <v>442</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D53" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E53" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="G53" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="H52" t="s">
-        <v>504</v>
-      </c>
-      <c r="I52">
-        <v>1</v>
-      </c>
-      <c r="J52" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K52" t="s">
+      <c r="H53" t="s">
+        <v>503</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K53" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="8">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="8">
         <v>1337</v>
       </c>
-      <c r="B53" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="C53" s="8" t="s">
+      <c r="B54" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="C54" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D54" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E54" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="F53" s="8" t="s">
+      <c r="F54" s="8" t="s">
         <v>181</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H53" t="s">
-        <v>185</v>
-      </c>
-      <c r="I53">
-        <v>1</v>
-      </c>
-      <c r="J53" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K53" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="8">
-        <v>1338</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>443</v>
       </c>
       <c r="G54" s="8" t="s">
         <v>184</v>
@@ -14855,27 +14667,24 @@
         <v>481</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>188</v>
+        <v>444</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>189</v>
+        <v>352</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>187</v>
+        <v>443</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H55" t="s">
         <v>185</v>
@@ -14887,24 +14696,27 @@
         <v>14</v>
       </c>
       <c r="K55" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="C56" s="11" t="s">
-        <v>446</v>
+      <c r="C56" s="8" t="s">
+        <v>188</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>354</v>
+        <v>189</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>445</v>
+        <v>187</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="G56" s="8" t="s">
         <v>190</v>
@@ -14922,184 +14734,181 @@
         <v>480</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>448</v>
+        <v>492</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>446</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>473</v>
+        <v>445</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="H57" t="s">
         <v>185</v>
       </c>
-      <c r="I57" s="8">
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K57" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="23">
+        <v>1345</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>448</v>
+      </c>
+      <c r="D58" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="E58" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="H58" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="I58" s="23">
         <v>0.1</v>
       </c>
-      <c r="J57" s="8" t="s">
+      <c r="J58" s="23" t="s">
         <v>447</v>
       </c>
-      <c r="K57" t="s">
+      <c r="K58" s="24" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="8">
+      <c r="L58" s="23" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="23">
+        <v>1350</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="C59" s="23" t="s">
+        <v>450</v>
+      </c>
+      <c r="D59" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="E59" s="27" t="s">
+        <v>449</v>
+      </c>
+      <c r="F59" s="23"/>
+      <c r="G59" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="H59" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="I59" s="23">
+        <v>1</v>
+      </c>
+      <c r="J59" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="K59" s="23" t="s">
+        <v>505</v>
+      </c>
+      <c r="L59" s="23"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="8">
+        <v>1350</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="H60" t="s">
+        <v>185</v>
+      </c>
+      <c r="I60" s="8">
+        <v>1</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="8">
         <v>1361</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C61" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D61" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E61" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="G58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H58" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I58" s="8">
-        <v>1</v>
-      </c>
-      <c r="J58" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K58" s="8" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="8">
-        <v>1368</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I59" s="8">
-        <v>1</v>
-      </c>
-      <c r="J59" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K59" s="8" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>1369</v>
-      </c>
-      <c r="B60" t="s">
-        <v>191</v>
-      </c>
-      <c r="C60" t="s">
-        <v>193</v>
-      </c>
-      <c r="D60" t="s">
-        <v>194</v>
-      </c>
-      <c r="E60" t="s">
-        <v>192</v>
-      </c>
-      <c r="F60" t="s">
-        <v>192</v>
-      </c>
-      <c r="G60" t="s">
-        <v>13</v>
-      </c>
-      <c r="H60" t="s">
-        <v>15</v>
-      </c>
-      <c r="I60" s="8">
-        <v>1</v>
-      </c>
-      <c r="J60" t="s">
-        <v>14</v>
-      </c>
-      <c r="K60" s="8" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>1379</v>
-      </c>
-      <c r="B61" t="s">
-        <v>191</v>
-      </c>
-      <c r="C61" t="s">
-        <v>463</v>
-      </c>
-      <c r="D61" t="s">
-        <v>195</v>
-      </c>
-      <c r="E61" t="s">
-        <v>464</v>
-      </c>
-      <c r="F61" t="s">
-        <v>464</v>
-      </c>
-      <c r="G61" t="s">
-        <v>13</v>
-      </c>
-      <c r="H61" t="s">
+      <c r="G61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" s="8" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="8">
         <v>1</v>
       </c>
-      <c r="J61" t="s">
+      <c r="J61" s="8" t="s">
         <v>14</v>
       </c>
       <c r="K61" s="8" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
-        <v>1382</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>196</v>
+        <v>1368</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>198</v>
+        <v>454</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>199</v>
+        <v>359</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>197</v>
+        <v>453</v>
       </c>
       <c r="G62" s="8" t="s">
         <v>13</v>
@@ -15117,85 +14926,94 @@
         <v>481</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="8">
-        <v>1383</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H63" s="8" t="s">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>1369</v>
+      </c>
+      <c r="B63" t="s">
+        <v>191</v>
+      </c>
+      <c r="C63" t="s">
+        <v>193</v>
+      </c>
+      <c r="D63" t="s">
+        <v>194</v>
+      </c>
+      <c r="E63" t="s">
+        <v>192</v>
+      </c>
+      <c r="F63" t="s">
+        <v>192</v>
+      </c>
+      <c r="G63" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="8">
         <v>1</v>
       </c>
-      <c r="J63" s="8" t="s">
+      <c r="J63" t="s">
         <v>14</v>
       </c>
       <c r="K63" s="8" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="8">
-        <v>1385</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H64" s="8" t="s">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>1379</v>
+      </c>
+      <c r="B64" t="s">
+        <v>191</v>
+      </c>
+      <c r="C64" t="s">
+        <v>463</v>
+      </c>
+      <c r="D64" t="s">
+        <v>195</v>
+      </c>
+      <c r="E64" t="s">
+        <v>464</v>
+      </c>
+      <c r="F64" t="s">
+        <v>464</v>
+      </c>
+      <c r="G64" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="8">
         <v>1</v>
       </c>
-      <c r="J64" s="8" t="s">
+      <c r="J64" t="s">
         <v>14</v>
       </c>
       <c r="K64" s="8" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G65" s="8" t="s">
         <v>13</v>
@@ -15213,24 +15031,21 @@
         <v>481</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>204</v>
+        <v>496</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>206</v>
+        <v>456</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>207</v>
+        <v>361</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>205</v>
+        <v>455</v>
       </c>
       <c r="G66" s="8" t="s">
         <v>13</v>
@@ -15248,24 +15063,18 @@
         <v>481</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
-        <v>1388</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>208</v>
+        <v>1385</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>210</v>
+        <v>458</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>211</v>
+        <v>362</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="F67" s="8" t="s">
-        <v>209</v>
+        <v>457</v>
       </c>
       <c r="G67" s="8" t="s">
         <v>13</v>
@@ -15283,24 +15092,24 @@
         <v>481</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="8">
-        <v>1392</v>
+        <v>1386</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="G68" s="8" t="s">
         <v>13</v>
@@ -15318,401 +15127,404 @@
         <v>481</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="8">
+        <v>1387</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I69" s="8">
+        <v>1</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K69" s="8" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" s="8">
+        <v>1388</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" s="8">
+        <v>1</v>
+      </c>
+      <c r="J70" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K70" s="8" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="8">
+        <v>1392</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" s="8">
+        <v>1</v>
+      </c>
+      <c r="J71" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K71" s="8" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" s="8">
         <v>1433</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B72" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C72" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D72" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E72" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F72" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="G69" s="8" t="s">
+      <c r="G72" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="H69" s="8" t="s">
+      <c r="H72" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="I69" s="8">
-        <v>1</v>
-      </c>
-      <c r="J69" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K69" t="s">
+      <c r="I72" s="8">
+        <v>1</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K72" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" s="8">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" s="8">
         <v>1439</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B73" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C73" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D73" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E73" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="F73" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="G70" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H70" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I70" s="8">
-        <v>1</v>
-      </c>
-      <c r="J70" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K70" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" s="8">
+      <c r="G73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I73" s="8">
+        <v>1</v>
+      </c>
+      <c r="J73" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K73" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="8">
         <v>1458</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B74" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C74" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="D71" s="8" t="s">
+      <c r="D74" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E74" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="F71" s="8" t="s">
+      <c r="F74" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="G71" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H71" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I71" s="8">
-        <v>1</v>
-      </c>
-      <c r="J71" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K71" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" s="8">
+      <c r="G74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" s="8">
+        <v>1</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K74" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" s="8">
         <v>1464</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B75" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C75" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="D75" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E75" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="F72" s="8" t="s">
+      <c r="F75" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="G72" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H72" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I72" s="8">
-        <v>1</v>
-      </c>
-      <c r="J72" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K72" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="8">
+      <c r="G75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I75" s="8">
+        <v>1</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K75" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" s="8">
         <v>1517</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B76" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C76" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="D76" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E76" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="F73" s="8" t="s">
+      <c r="F76" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="G73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H73" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I73" s="8">
-        <v>1</v>
-      </c>
-      <c r="J73" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K73" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="8">
+      <c r="G76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I76" s="8">
+        <v>1</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K76" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77" s="8">
         <v>1551</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B77" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C77" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="D77" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E77" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="G74" s="8" t="s">
+      <c r="G77" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="H74" s="8" t="s">
+      <c r="H77" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="I74" s="8">
-        <v>1</v>
-      </c>
-      <c r="J74" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K74" t="s">
+      <c r="I77" s="8">
+        <v>1</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K77" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" s="8">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" s="8">
         <v>1551</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B78" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C78" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="D75" s="8" t="s">
+      <c r="D78" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="E75" s="8" t="s">
+      <c r="E78" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="G75" s="8" t="s">
+      <c r="G78" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="H75" s="8" t="s">
+      <c r="H78" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="I75" s="8">
-        <v>1</v>
-      </c>
-      <c r="J75" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K75" s="8" t="s">
+      <c r="I78" s="8">
+        <v>1</v>
+      </c>
+      <c r="J78" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K78" s="8" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="8">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79" s="8">
         <v>1629</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B79" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C79" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="D76" s="8" t="s">
+      <c r="D79" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="E76" s="8" t="s">
+      <c r="E79" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="F76" s="8" t="s">
+      <c r="F79" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="G76" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H76" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I76" s="8">
-        <v>1</v>
-      </c>
-      <c r="J76" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K76" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" s="8">
+      <c r="G79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" s="8">
+        <v>1</v>
+      </c>
+      <c r="J79" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K79" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80" s="8">
         <v>1630</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B80" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C80" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="D77" s="8" t="s">
+      <c r="D80" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="E77" s="8" t="s">
+      <c r="E80" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="F77" s="8" t="s">
+      <c r="F80" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="G77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H77" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I77" s="8">
-        <v>1</v>
-      </c>
-      <c r="J77" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K77" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="8">
-        <v>1652</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H78" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I78" s="8">
-        <v>1</v>
-      </c>
-      <c r="J78" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K78" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" s="8">
-        <v>1688</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H79" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I79" s="8">
-        <v>1</v>
-      </c>
-      <c r="J79" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K79" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" s="8">
-        <v>1774</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="E80" t="s">
-        <v>242</v>
-      </c>
       <c r="G80" s="8" t="s">
         <v>13</v>
       </c>
@@ -15727,26 +15539,26 @@
       </c>
       <c r="K80" s="8" t="s">
         <v>473</v>
-      </c>
-      <c r="L80" s="8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="8">
-        <v>1774</v>
+        <v>1652</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>371</v>
+        <v>245</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>373</v>
+        <v>247</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>374</v>
+        <v>248</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>169</v>
+        <v>246</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>246</v>
       </c>
       <c r="G81" s="8" t="s">
         <v>13</v>
@@ -15762,169 +15574,154 @@
       </c>
       <c r="K81" s="8" t="s">
         <v>473</v>
-      </c>
-      <c r="L81" s="8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="8">
+        <v>1688</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" s="8">
+        <v>1</v>
+      </c>
+      <c r="J82" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K82" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="8">
         <v>1774</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B83" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C83" t="s">
         <v>373</v>
       </c>
-      <c r="D82" s="8" t="s">
+      <c r="D83" t="s">
         <v>374</v>
       </c>
-      <c r="E82" t="s">
-        <v>238</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H82" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I82" s="8">
-        <v>1</v>
-      </c>
-      <c r="J82" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K82" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="L82" s="8" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="8">
+      <c r="E83" t="s">
+        <v>372</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L83" s="8" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="8">
         <v>1877</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B84" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C84" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D83" s="8" t="s">
+      <c r="D84" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="E83" s="8" t="s">
+      <c r="E84" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="F83" s="8" t="s">
+      <c r="F84" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="G83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H83" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I83" s="8">
-        <v>1</v>
-      </c>
-      <c r="J83" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K83" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A84" s="8">
+      <c r="G84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" s="8">
+        <v>1</v>
+      </c>
+      <c r="J84" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K84" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" s="8">
         <v>1888</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B85" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="C84" s="9" t="s">
+      <c r="C85" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="D84" s="8" t="s">
+      <c r="D85" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="E84" s="8" t="s">
+      <c r="E85" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F84" s="8" t="s">
+      <c r="F85" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="G84" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H84" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I84" s="8">
-        <v>1</v>
-      </c>
-      <c r="J84" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K84" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="8">
+      <c r="G85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H85" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" s="8">
+        <v>1</v>
+      </c>
+      <c r="J85" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K85" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="8">
         <v>1935</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B86" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C86" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="D85" s="8" t="s">
+      <c r="D86" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="E85" s="8" t="s">
+      <c r="E86" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="F85" s="8" t="s">
+      <c r="F86" s="8" t="s">
         <v>260</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H85" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I85" s="8">
-        <v>1</v>
-      </c>
-      <c r="J85" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K85" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A86" s="8">
-        <v>1959</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="C86" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="E86" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="F86" s="8" t="s">
-        <v>264</v>
       </c>
       <c r="G86" s="8" t="s">
         <v>13</v>
@@ -15944,22 +15741,22 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="8">
-        <v>2028</v>
+        <v>1959</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>269</v>
+        <v>263</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>265</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="G87" s="8" t="s">
         <v>13</v>
@@ -15979,92 +15776,92 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="8">
+        <v>2028</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" s="8">
+        <v>1</v>
+      </c>
+      <c r="J88" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K88" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" s="8">
         <v>2879</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B89" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="C88" s="8" t="s">
+      <c r="C89" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="D88" s="8" t="s">
+      <c r="D89" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="E88" s="8" t="s">
+      <c r="E89" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="F88" s="8" t="s">
+      <c r="F89" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="G88" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H88" s="8" t="s">
+      <c r="G89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H89" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="I88" s="8">
+      <c r="I89" s="8">
         <v>1E-3</v>
       </c>
-      <c r="J88" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K88" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="8">
+      <c r="J89" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K89" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="8">
         <v>2911</v>
       </c>
-      <c r="B89" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="C89" s="8" t="s">
+      <c r="B90" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="C90" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="D89" s="8" t="s">
+      <c r="D90" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="E89" s="8" t="s">
+      <c r="E90" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="F89" s="8" t="s">
+      <c r="F90" s="8" t="s">
         <v>277</v>
-      </c>
-      <c r="G89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H89" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" s="8">
-        <v>1</v>
-      </c>
-      <c r="J89" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K89" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A90" s="8">
-        <v>2912</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="E90" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F90" s="8" t="s">
-        <v>281</v>
       </c>
       <c r="G90" s="8" t="s">
         <v>13</v>
@@ -16084,22 +15881,22 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="8">
-        <v>2915</v>
+        <v>2912</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>281</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G91" s="8" t="s">
         <v>13</v>
@@ -16119,22 +15916,22 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="8">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G92" s="8" t="s">
         <v>13</v>
@@ -16154,22 +15951,22 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="8">
-        <v>2919</v>
+        <v>2916</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="G93" s="8" t="s">
         <v>13</v>
@@ -16189,22 +15986,22 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="8">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G94" s="8" t="s">
         <v>13</v>
@@ -16224,25 +16021,25 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="8">
-        <v>5347</v>
+        <v>2920</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>472</v>
+        <v>13</v>
       </c>
       <c r="H95" s="8" t="s">
         <v>15</v>
@@ -16259,27 +16056,30 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="8">
-        <v>5534</v>
+        <v>5347</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>469</v>
+        <v>300</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>460</v>
+        <v>302</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="E96" t="s">
-        <v>21</v>
+        <v>301</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>301</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H96" t="s">
-        <v>15</v>
-      </c>
-      <c r="I96">
+        <v>472</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I96" s="8">
         <v>1</v>
       </c>
       <c r="J96" s="8" t="s">
@@ -16287,34 +16087,31 @@
       </c>
       <c r="K96" s="8" t="s">
         <v>473</v>
-      </c>
-      <c r="L96" s="8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="8">
-        <v>5534</v>
+        <v>5474</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>469</v>
+        <v>386</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>460</v>
+        <v>388</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="E97" t="s">
-        <v>102</v>
+        <v>389</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>506</v>
       </c>
       <c r="G97" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H97" t="s">
-        <v>15</v>
-      </c>
-      <c r="I97">
+      <c r="H97" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="8">
         <v>1</v>
       </c>
       <c r="J97" s="8" t="s">
@@ -16322,9 +16119,6 @@
       </c>
       <c r="K97" s="8" t="s">
         <v>473</v>
-      </c>
-      <c r="L97" s="8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
@@ -16341,76 +16135,66 @@
         <v>390</v>
       </c>
       <c r="E98" t="s">
-        <v>86</v>
+        <v>459</v>
       </c>
       <c r="G98" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H98" t="s">
-        <v>15</v>
-      </c>
-      <c r="I98">
-        <v>1</v>
-      </c>
-      <c r="J98" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K98" s="8" t="s">
-        <v>473</v>
-      </c>
+      <c r="H98"/>
+      <c r="I98"/>
       <c r="L98" s="8" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="8">
-        <v>5534</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>469</v>
+        <v>5977</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="E99" t="s">
-        <v>141</v>
-      </c>
-      <c r="G99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H99" t="s">
-        <v>15</v>
-      </c>
-      <c r="I99">
-        <v>1</v>
+        <v>395</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="G99" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I99" s="8">
+        <v>1000</v>
       </c>
       <c r="J99" s="8" t="s">
         <v>14</v>
       </c>
       <c r="K99" s="8" t="s">
         <v>473</v>
-      </c>
-      <c r="L99" s="8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="8">
-        <v>5977</v>
+        <v>5978</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>303</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>462</v>
+        <v>305</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>395</v>
+        <v>304</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="G100" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="G100" s="17" t="s">
         <v>472</v>
       </c>
       <c r="H100" s="8" t="s">
@@ -16426,26 +16210,26 @@
         <v>473</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="8">
-        <v>5978</v>
+        <v>5979</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="G101" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="G101" s="17" t="s">
         <v>472</v>
       </c>
       <c r="H101" s="8" t="s">
@@ -16462,58 +16246,54 @@
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A102" s="8">
-        <v>5979</v>
-      </c>
-      <c r="B102" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="D102" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="E102" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F102" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="G102" s="18" t="s">
+      <c r="A102" s="22">
+        <v>6561</v>
+      </c>
+      <c r="B102" s="23" t="s">
+        <v>396</v>
+      </c>
+      <c r="C102" t="s">
+        <v>398</v>
+      </c>
+      <c r="D102" t="s">
+        <v>399</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="F102" s="23"/>
+      <c r="G102" s="25" t="s">
         <v>472</v>
       </c>
-      <c r="H102" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I102" s="8">
-        <v>1000</v>
-      </c>
-      <c r="J102" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K102" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="20">
-        <v>6561</v>
+      <c r="H102" s="23"/>
+      <c r="I102" s="23"/>
+      <c r="J102" s="23"/>
+      <c r="K102" s="23"/>
+      <c r="L102" s="23" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A103" s="8">
+        <v>6616</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>396</v>
+        <v>310</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>398</v>
+        <v>312</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="E103" t="s">
-        <v>488</v>
-      </c>
-      <c r="G103" s="18" t="s">
-        <v>472</v>
+        <v>313</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="H103" s="8" t="s">
         <v>15</v>
@@ -16527,27 +16307,27 @@
       <c r="K103" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="L103" s="8" t="s">
-        <v>490</v>
-      </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A104" s="20">
-        <v>6561</v>
+      <c r="A104" s="8">
+        <v>6830</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>396</v>
+        <v>314</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>398</v>
+        <v>316</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="E104" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="G104" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="G104" s="17" t="s">
         <v>472</v>
       </c>
       <c r="H104" s="8" t="s">
@@ -16562,37 +16342,34 @@
       <c r="K104" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="L104" s="8" t="s">
-        <v>490</v>
-      </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="8">
-        <v>6616</v>
+        <v>7073</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>13</v>
+        <v>184</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="I105" s="8">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="J105" s="8" t="s">
         <v>14</v>
@@ -16601,59 +16378,47 @@
         <v>473</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A106" s="8">
-        <v>6830</v>
+    <row r="106" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="18" t="s">
+        <v>409</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>317</v>
+        <v>410</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="F106" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="G106" s="18" t="s">
-        <v>472</v>
+        <v>504</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>184</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="I106" s="8">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="J106" s="8" t="s">
         <v>14</v>
       </c>
       <c r="K106" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A107" s="8">
-        <v>7073</v>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="18" t="s">
+        <v>411</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>320</v>
+        <v>469</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>321</v>
+        <v>412</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="F107" s="8" t="s">
-        <v>319</v>
+        <v>490</v>
       </c>
       <c r="G107" s="8" t="s">
         <v>184</v>
@@ -16671,75 +16436,82 @@
         <v>473</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="20" t="s">
-        <v>409</v>
-      </c>
-      <c r="B108" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="D108" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="E108" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="G108" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H108" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="I108" s="8">
-        <v>1</v>
-      </c>
-      <c r="J108" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K108" s="8" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="20" t="s">
-        <v>411</v>
-      </c>
-      <c r="B109" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="D109" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="E109" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="G109" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="H109" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="I109" s="8">
-        <v>1</v>
-      </c>
-      <c r="J109" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K109" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A116"/>
-      <c r="B116"/>
-      <c r="C116"/>
-      <c r="D116"/>
-      <c r="E116"/>
-      <c r="F116"/>
-      <c r="G116"/>
-      <c r="H116"/>
-      <c r="I116"/>
-      <c r="J116"/>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A108" s="22" t="s">
+        <v>507</v>
+      </c>
+      <c r="B108" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="C108" s="23"/>
+      <c r="D108" s="23" t="s">
+        <v>415</v>
+      </c>
+      <c r="E108" s="23"/>
+      <c r="F108" s="23"/>
+      <c r="G108" s="25" t="s">
+        <v>497</v>
+      </c>
+      <c r="H108" s="23"/>
+      <c r="I108" s="23"/>
+      <c r="J108" s="23"/>
+      <c r="K108" s="23"/>
+      <c r="L108" s="23" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A109" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="B109" s="23" t="s">
+        <v>417</v>
+      </c>
+      <c r="C109" s="23"/>
+      <c r="D109" s="23" t="s">
+        <v>418</v>
+      </c>
+      <c r="E109" s="23"/>
+      <c r="F109" s="23"/>
+      <c r="G109" s="25" t="s">
+        <v>497</v>
+      </c>
+      <c r="H109" s="23"/>
+      <c r="I109" s="23"/>
+      <c r="J109" s="23"/>
+      <c r="K109" s="23"/>
+      <c r="L109" s="23" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A110" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="B110" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="C110" s="23"/>
+      <c r="D110" s="23" t="s">
+        <v>423</v>
+      </c>
+      <c r="E110" s="23"/>
+      <c r="F110" s="23"/>
+      <c r="G110" s="25" t="s">
+        <v>497</v>
+      </c>
+      <c r="H110" s="23"/>
+      <c r="I110" s="23"/>
+      <c r="J110" s="23"/>
+      <c r="K110" s="23"/>
+      <c r="L110" s="23" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C114" s="4"/>
+      <c r="D114" s="2"/>
+      <c r="E114"/>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117"/>
@@ -16753,6 +16525,14 @@
       <c r="I117"/>
       <c r="J117"/>
     </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A118"/>
+      <c r="B118"/>
+      <c r="G118"/>
+      <c r="H118"/>
+      <c r="I118"/>
+      <c r="J118"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16760,7 +16540,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970266C0-8727-44C2-B81E-9D7925A7C18F}">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.88671875" style="8" customWidth="1"/>
@@ -16805,13 +16585,13 @@
       <c r="H1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="17" t="s">
-        <v>501</v>
+      <c r="I1" s="16" t="s">
+        <v>500</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="15" t="s">
         <v>474</v>
       </c>
       <c r="L1" s="10" t="s">
@@ -16904,25 +16684,23 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
-        <v>1198</v>
+        <v>1314</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>114</v>
+        <v>335</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>438</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>115</v>
+        <v>347</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>113</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="F5" s="12"/>
       <c r="G5" s="12" t="s">
-        <v>13</v>
+        <v>471</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
@@ -16934,51 +16712,51 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>335</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>347</v>
+        <v>439</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12" t="s">
-        <v>471</v>
+        <v>184</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
+      <c r="K6" s="19"/>
       <c r="L6" s="12" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
-        <v>1319</v>
+        <v>1743</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>440</v>
+        <v>367</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>369</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>439</v>
+        <v>368</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
@@ -16988,25 +16766,25 @@
         <v>467</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12">
-        <v>1350</v>
+        <v>1920</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>450</v>
+        <v>375</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>377</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>449</v>
+        <v>378</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>376</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12" t="s">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
@@ -17018,19 +16796,19 @@
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12">
-        <v>1743</v>
+        <v>1955</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>369</v>
+        <v>379</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>381</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12" t="s">
@@ -17044,21 +16822,21 @@
         <v>467</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="12">
-        <v>1920</v>
+        <v>1958</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="s">
@@ -17072,21 +16850,21 @@
         <v>467</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="12">
-        <v>1955</v>
+        <v>5537</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>381</v>
+        <v>391</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>393</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="12" t="s">
@@ -17102,20 +16880,16 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="12">
-        <v>1958</v>
+        <v>6678</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>385</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="C12" s="12"/>
       <c r="D12" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>384</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12" t="s">
         <v>13</v>
@@ -17130,25 +16904,21 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="12">
-        <v>5474</v>
+        <v>6678</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>388</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="C13" s="12"/>
       <c r="D13" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>387</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="12"/>
+      <c r="H13" s="19"/>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
@@ -17158,19 +16928,19 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="12">
-        <v>5537</v>
+        <v>7128</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12" t="s">
@@ -17186,18 +16956,16 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="12">
-        <v>6678</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>400</v>
-      </c>
+        <v>7170</v>
+      </c>
+      <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="12" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="12"/>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="12" t="s">
         <v>13</v>
       </c>
       <c r="H15" s="12"/>
@@ -17210,19 +16978,19 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="12">
-        <v>6678</v>
+        <v>7706</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>469</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="19" t="s">
-        <v>13</v>
+      <c r="G16" s="12" t="s">
+        <v>512</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
@@ -17232,175 +17000,29 @@
         <v>467</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="12">
-        <v>7128</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>406</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="12">
-        <v>7170</v>
-      </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="12">
-        <v>7706</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>469</v>
-      </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12" t="s">
-        <v>408</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29"/>
-      <c r="B29"/>
-      <c r="C29"/>
-      <c r="D29"/>
-      <c r="E29"/>
-      <c r="F29"/>
-      <c r="G29"/>
-      <c r="H29"/>
-      <c r="I29"/>
-      <c r="J29"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
-      <c r="I30"/>
-      <c r="J30"/>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
